--- a/PAMaap/app/archives/public/Enero/CPU y Memoria/ARUS - AD-MIEMBROS - CPU Load & Memory Used (Last Month).xlsx
+++ b/PAMaap/app/archives/public/Enero/CPU y Memoria/ARUS - AD-MIEMBROS - CPU Load & Memory Used (Last Month).xlsx
@@ -14,15 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="264">
-  <si>
-    <t>9.36 GB</t>
-  </si>
-  <si>
-    <t>3.90 %</t>
-  </si>
-  <si>
-    <t>5.24 GB</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="283">
+  <si>
+    <t>8.39 GB</t>
+  </si>
+  <si>
+    <t>19.88 %</t>
   </si>
   <si>
     <t>10.200.152.53</t>
@@ -31,43 +28,31 @@
     <t>7.45 %</t>
   </si>
   <si>
-    <t>4.93 GB</t>
-  </si>
-  <si>
-    <t>4.99 GB</t>
-  </si>
-  <si>
-    <t>20.67 %</t>
-  </si>
-  <si>
-    <t>7.77 GB</t>
-  </si>
-  <si>
-    <t>6.41 GB</t>
+    <t>2.90 GB</t>
+  </si>
+  <si>
+    <t>14.53 GB</t>
+  </si>
+  <si>
+    <t>39.00 %</t>
   </si>
   <si>
     <t>SRFTP04</t>
   </si>
   <si>
-    <t>3.24 GB</t>
-  </si>
-  <si>
     <t>ARLMDEPISO8</t>
   </si>
   <si>
-    <t>3.19 GB</t>
-  </si>
-  <si>
-    <t>21.90 %</t>
-  </si>
-  <si>
-    <t>71.31 %</t>
+    <t>26.11 %</t>
+  </si>
+  <si>
+    <t>38.31 %</t>
   </si>
   <si>
     <t>10.209.45.241</t>
   </si>
   <si>
-    <t>7.64 GB</t>
+    <t>9.55 GB</t>
   </si>
   <si>
     <t>10.205.30.203</t>
@@ -76,16 +61,13 @@
     <t>Windows 2019 Server</t>
   </si>
   <si>
-    <t>6.76 GB</t>
-  </si>
-  <si>
-    <t>56.33 %</t>
-  </si>
-  <si>
-    <t>5.98 GB</t>
-  </si>
-  <si>
-    <t>5.52 GB</t>
+    <t>5.26 GB</t>
+  </si>
+  <si>
+    <t>3.69 GB</t>
+  </si>
+  <si>
+    <t>5.54 GB</t>
   </si>
   <si>
     <t>MDESEGU2</t>
@@ -94,64 +76,61 @@
     <t>10.216.24.190</t>
   </si>
   <si>
+    <t>5.86 GB</t>
+  </si>
+  <si>
     <t>Minimum Memory Used</t>
   </si>
   <si>
-    <t>11.78 GB</t>
-  </si>
-  <si>
-    <t>44.05 %</t>
-  </si>
-  <si>
-    <t>0.61 %</t>
+    <t>5.11 GB</t>
+  </si>
+  <si>
+    <t>4.45 GB</t>
+  </si>
+  <si>
+    <t>49.91 %</t>
+  </si>
+  <si>
+    <t>5.63 GB</t>
+  </si>
+  <si>
+    <t>3.96 %</t>
   </si>
   <si>
     <t>SRISSUINGCA02</t>
   </si>
   <si>
-    <t>3.09 %</t>
+    <t>5.55 GB</t>
   </si>
   <si>
     <t>10.205.30.17</t>
   </si>
   <si>
-    <t>4.48 %</t>
-  </si>
-  <si>
-    <t>44.74 GB</t>
-  </si>
-  <si>
-    <t>44.21 %</t>
-  </si>
-  <si>
-    <t>37.48 %</t>
-  </si>
-  <si>
-    <t>2.16 %</t>
+    <t>20.00 %</t>
   </si>
   <si>
     <t>10.204.4.227</t>
   </si>
   <si>
+    <t>6.27 GB</t>
+  </si>
+  <si>
     <t>BOGSEGU5</t>
   </si>
   <si>
-    <t>11.43 %</t>
-  </si>
-  <si>
-    <t>7.63 %</t>
-  </si>
-  <si>
     <t>SRMESAP01</t>
   </si>
   <si>
     <t>SSFILP02</t>
   </si>
   <si>
-    <t>3.26 %</t>
-  </si>
-  <si>
-    <t>98.00 %</t>
+    <t>30.94 %</t>
+  </si>
+  <si>
+    <t>12.30 GB</t>
+  </si>
+  <si>
+    <t>36.00 %</t>
   </si>
   <si>
     <t>Windows 2016 Server</t>
@@ -166,22 +145,25 @@
     <t>10.201.138.71</t>
   </si>
   <si>
-    <t>2.57 GB</t>
-  </si>
-  <si>
-    <t>37.60 %</t>
-  </si>
-  <si>
-    <t>12.96 %</t>
+    <t>4.81 GB</t>
+  </si>
+  <si>
+    <t>2.88 %</t>
   </si>
   <si>
     <t>10.203.90.56</t>
   </si>
   <si>
-    <t>48.96 %</t>
-  </si>
-  <si>
-    <t>8.22 GB</t>
+    <t>2.18 GB</t>
+  </si>
+  <si>
+    <t>6.12 GB</t>
+  </si>
+  <si>
+    <t>15.61 %</t>
+  </si>
+  <si>
+    <t>39.42 %</t>
   </si>
   <si>
     <t>SGFILP01</t>
@@ -190,73 +172,103 @@
     <t>10.205.30.202</t>
   </si>
   <si>
-    <t>76.43 %</t>
-  </si>
-  <si>
-    <t>25.13 %</t>
+    <t>83.00 %</t>
+  </si>
+  <si>
+    <t>47.64 %</t>
+  </si>
+  <si>
+    <t>23.33 %</t>
+  </si>
+  <si>
+    <t>36.38 %</t>
   </si>
   <si>
     <t>10.200.152.38</t>
   </si>
   <si>
-    <t>43.86 %</t>
-  </si>
-  <si>
-    <t>6.16 %</t>
-  </si>
-  <si>
-    <t>5.66 GB</t>
+    <t>4.77 GB</t>
+  </si>
+  <si>
+    <t>8.08 GB</t>
+  </si>
+  <si>
+    <t>2.45 %</t>
+  </si>
+  <si>
+    <t>0.86 %</t>
+  </si>
+  <si>
+    <t>4.37 GB</t>
   </si>
   <si>
     <t>Sede</t>
   </si>
   <si>
-    <t>8.31 GB</t>
-  </si>
-  <si>
     <t>SGCLOFILP01</t>
   </si>
   <si>
-    <t>3.32 GB</t>
+    <t>7.36 GB</t>
+  </si>
+  <si>
+    <t>40.20 %</t>
   </si>
   <si>
     <t>SRFTP01</t>
   </si>
   <si>
-    <t>5.22 GB</t>
+    <t>3.14 GB</t>
+  </si>
+  <si>
+    <t>12.11 GB</t>
+  </si>
+  <si>
+    <t>59.00 %</t>
   </si>
   <si>
     <t>5.43 GB</t>
   </si>
   <si>
-    <t>7.49 GB</t>
-  </si>
-  <si>
-    <t>4.55 GB</t>
-  </si>
-  <si>
-    <t>26.00 %</t>
-  </si>
-  <si>
-    <t>8.18 GB</t>
-  </si>
-  <si>
-    <t>5.81 GB</t>
+    <t>10.10 GB</t>
+  </si>
+  <si>
+    <t>6.15 GB</t>
+  </si>
+  <si>
+    <t>SRSAFTP03</t>
+  </si>
+  <si>
+    <t>3.48 GB</t>
+  </si>
+  <si>
+    <t>21.00 %</t>
+  </si>
+  <si>
+    <t>6.79 GB</t>
+  </si>
+  <si>
+    <t>15.91 GB</t>
+  </si>
+  <si>
+    <t>3.38 %</t>
+  </si>
+  <si>
+    <t>44.29 %</t>
+  </si>
+  <si>
+    <t>5.59 GB</t>
   </si>
   <si>
     <t>10.204.4.59</t>
   </si>
   <si>
-    <t>3.03 GB</t>
-  </si>
-  <si>
     <t>Average Memory Used</t>
   </si>
   <si>
-    <t>62.00 %</t>
-  </si>
-  <si>
-    <t>85.00 %</t>
+    <t>7.54 GB</t>
+  </si>
+  <si>
+    <t>79.95 %</t>
   </si>
   <si>
     <t>CENTRO DE COMPUTO IBM BOGOTA</t>
@@ -265,13 +277,22 @@
     <t>GPO ONE PLAZA MEDELLIN</t>
   </si>
   <si>
+    <t>41.22 %</t>
+  </si>
+  <si>
+    <t>8.87 GB</t>
+  </si>
+  <si>
     <t>10.202.4.84</t>
   </si>
   <si>
+    <t>5.06 %</t>
+  </si>
+  <si>
     <t>3.18 GB</t>
   </si>
   <si>
-    <t>47.36 %</t>
+    <t>10.53.56.4</t>
   </si>
   <si>
     <t>SRFTP02</t>
@@ -280,40 +301,43 @@
     <t>10.205.30.201</t>
   </si>
   <si>
-    <t>5.38 GB</t>
-  </si>
-  <si>
-    <t>4.28 GB</t>
-  </si>
-  <si>
-    <t>39.22 %</t>
+    <t>9.29 GB</t>
+  </si>
+  <si>
+    <t>SRMDEFIL06</t>
   </si>
   <si>
     <t>SGCLOFILP02</t>
   </si>
   <si>
-    <t>9.40 GB</t>
+    <t>4.10 GB</t>
   </si>
   <si>
     <t>SRFTPFSL01</t>
   </si>
   <si>
-    <t>27.12 GB</t>
-  </si>
-  <si>
-    <t>7.68 GB</t>
-  </si>
-  <si>
-    <t>38.00 %</t>
+    <t>22.69 %</t>
+  </si>
+  <si>
+    <t>7.98 GB</t>
+  </si>
+  <si>
+    <t>51.27 %</t>
+  </si>
+  <si>
+    <t>41.47 %</t>
   </si>
   <si>
     <t>SRFTPL01</t>
   </si>
   <si>
-    <t>43.20 %</t>
-  </si>
-  <si>
-    <t>2.19 GB</t>
+    <t>6.72 GB</t>
+  </si>
+  <si>
+    <t>30.00 %</t>
+  </si>
+  <si>
+    <t>5.97 GB</t>
   </si>
   <si>
     <t>ARL REGIONAL CALI</t>
@@ -322,16 +346,19 @@
     <t>6.84 GB</t>
   </si>
   <si>
-    <t>5.73 %</t>
+    <t>44.95 %</t>
+  </si>
+  <si>
+    <t>48.00 %</t>
+  </si>
+  <si>
+    <t>7.78 %</t>
   </si>
   <si>
     <t>MDESEGU1</t>
   </si>
   <si>
-    <t>4.95 GB</t>
-  </si>
-  <si>
-    <t>2.97 GB</t>
+    <t>1.05 %</t>
   </si>
   <si>
     <t>10.200.152.39</t>
@@ -340,10 +367,19 @@
     <t>SRVBADI02</t>
   </si>
   <si>
+    <t>7.86 GB</t>
+  </si>
+  <si>
     <t>Average Percent Memory Used</t>
   </si>
   <si>
-    <t>5.41 GB</t>
+    <t>61.03 %</t>
+  </si>
+  <si>
+    <t>2.30 GB</t>
+  </si>
+  <si>
+    <t>0.99 %</t>
   </si>
   <si>
     <t>Peak CPU Load</t>
@@ -352,58 +388,61 @@
     <t>29.00 %</t>
   </si>
   <si>
-    <t>7.03 GB</t>
-  </si>
-  <si>
     <t>10.205.31.66</t>
   </si>
   <si>
+    <t>SRFTPD03</t>
+  </si>
+  <si>
+    <t>3.57 GB</t>
+  </si>
+  <si>
+    <t>1.84 %</t>
+  </si>
+  <si>
     <t>10.209.8.251</t>
   </si>
   <si>
+    <t>64.75 %</t>
+  </si>
+  <si>
     <t>3.76 GB</t>
   </si>
   <si>
-    <t>9.88 GB</t>
-  </si>
-  <si>
-    <t>27.75 %</t>
+    <t>7.92 GB</t>
+  </si>
+  <si>
+    <t>0.39 %</t>
+  </si>
+  <si>
+    <t>0.95 %</t>
   </si>
   <si>
     <t>CAMPUS TORRE SURAMERICANA MEDELLIN</t>
   </si>
   <si>
-    <t>3.88 GB</t>
+    <t>79.61 %</t>
   </si>
   <si>
     <t>10.205.30.200</t>
   </si>
   <si>
-    <t>7.07 GB</t>
-  </si>
-  <si>
     <t>10.209.39.248</t>
   </si>
   <si>
-    <t>7.41 GB</t>
-  </si>
-  <si>
-    <t>4.67 GB</t>
-  </si>
-  <si>
-    <t>5.25 GB</t>
-  </si>
-  <si>
-    <t>January 2026</t>
-  </si>
-  <si>
-    <t>13.10 %</t>
-  </si>
-  <si>
-    <t>21.96 GB</t>
-  </si>
-  <si>
-    <t>5.40 GB</t>
+    <t>41.20 %</t>
+  </si>
+  <si>
+    <t>21.24 %</t>
+  </si>
+  <si>
+    <t>4.76 GB</t>
+  </si>
+  <si>
+    <t>0.40 %</t>
+  </si>
+  <si>
+    <t>24.75 %</t>
   </si>
   <si>
     <t>SRTSLICL01</t>
@@ -412,49 +451,58 @@
     <t>10.205.30.16</t>
   </si>
   <si>
-    <t>8.88 %</t>
-  </si>
-  <si>
-    <t>2.71 %</t>
+    <t>6.42 %</t>
+  </si>
+  <si>
+    <t>56.81 %</t>
+  </si>
+  <si>
+    <t>6.37 GB</t>
   </si>
   <si>
     <t>10.211.2.80</t>
   </si>
   <si>
-    <t>6.68 GB</t>
-  </si>
-  <si>
     <t>100.00 %</t>
   </si>
   <si>
-    <t>7.02 GB</t>
-  </si>
-  <si>
-    <t>3.15 GB</t>
-  </si>
-  <si>
-    <t>8.06 GB</t>
+    <t>6.86 GB</t>
   </si>
   <si>
     <t>10.216.24.250</t>
   </si>
   <si>
-    <t>67.25 %</t>
-  </si>
-  <si>
-    <t>45.68 %</t>
-  </si>
-  <si>
-    <t>3.53 GB</t>
-  </si>
-  <si>
-    <t>74.00 %</t>
-  </si>
-  <si>
-    <t>2.99 GB</t>
-  </si>
-  <si>
-    <t>13.79 GB</t>
+    <t>69.29 %</t>
+  </si>
+  <si>
+    <t>25.63 %</t>
+  </si>
+  <si>
+    <t>25.02 %</t>
+  </si>
+  <si>
+    <t>13.97 GB</t>
+  </si>
+  <si>
+    <t>3.89 %</t>
+  </si>
+  <si>
+    <t>1.56 %</t>
+  </si>
+  <si>
+    <t>47.10 %</t>
+  </si>
+  <si>
+    <t>2.12 GB</t>
+  </si>
+  <si>
+    <t>94.00 %</t>
+  </si>
+  <si>
+    <t>2.01 %</t>
+  </si>
+  <si>
+    <t>3.20 GB</t>
   </si>
   <si>
     <t>10.201.121.31</t>
@@ -463,34 +511,25 @@
     <t>10.207.25.20</t>
   </si>
   <si>
-    <t>75.86 %</t>
-  </si>
-  <si>
-    <t>12.90 GB</t>
-  </si>
-  <si>
-    <t>3.58 GB</t>
-  </si>
-  <si>
-    <t>2.51 %</t>
+    <t>7.79 GB</t>
+  </si>
+  <si>
+    <t>42.02 %</t>
+  </si>
+  <si>
+    <t>9.90 GB</t>
+  </si>
+  <si>
+    <t>2.95 GB</t>
+  </si>
+  <si>
+    <t>13.14 %</t>
   </si>
   <si>
     <t>SRASSESMENTP01</t>
   </si>
   <si>
-    <t>20.85 %</t>
-  </si>
-  <si>
-    <t>1.58 %</t>
-  </si>
-  <si>
-    <t>18.00 %</t>
-  </si>
-  <si>
-    <t>3.29 GB</t>
-  </si>
-  <si>
-    <t>2.43 GB</t>
+    <t>3.73 GB</t>
   </si>
   <si>
     <t>10.205.30.53</t>
@@ -499,52 +538,61 @@
     <t>SRFTP03</t>
   </si>
   <si>
+    <t>4.71 GB</t>
+  </si>
+  <si>
     <t>10.201.30.204</t>
   </si>
   <si>
-    <t>0.68 %</t>
+    <t>27.41 GB</t>
+  </si>
+  <si>
+    <t>2.27 GB</t>
   </si>
   <si>
     <t>SRMDEFIL08</t>
   </si>
   <si>
-    <t>7.59 GB</t>
-  </si>
-  <si>
-    <t>13.78 GB</t>
+    <t>6.01 GB</t>
+  </si>
+  <si>
+    <t>4.94 GB</t>
+  </si>
+  <si>
+    <t>3.33 GB</t>
+  </si>
+  <si>
+    <t>0.34 %</t>
+  </si>
+  <si>
+    <t>4.17 GB</t>
   </si>
   <si>
     <t>Windows 2022 Server</t>
   </si>
   <si>
-    <t>81.04 %</t>
+    <t>2.98 GB</t>
   </si>
   <si>
     <t>SRFLCLUP02</t>
   </si>
   <si>
-    <t>15.00 %</t>
-  </si>
-  <si>
-    <t>65.45 %</t>
-  </si>
-  <si>
-    <t>4.51 GB</t>
-  </si>
-  <si>
-    <t>45.19 %</t>
-  </si>
-  <si>
-    <t>5.95 GB</t>
+    <t>7.44 GB</t>
+  </si>
+  <si>
+    <t>8.85 GB</t>
+  </si>
+  <si>
+    <t>3.65 GB</t>
+  </si>
+  <si>
+    <t>February 2026</t>
   </si>
   <si>
     <t>7.40 GB</t>
   </si>
   <si>
-    <t>62.35 %</t>
-  </si>
-  <si>
-    <t>4.18 GB</t>
+    <t>19.38 GB</t>
   </si>
   <si>
     <t>SRMDEFIL07</t>
@@ -556,244 +604,250 @@
     <t>IP Address</t>
   </si>
   <si>
+    <t>68.67 %</t>
+  </si>
+  <si>
     <t>SRFLCLUP01</t>
   </si>
   <si>
-    <t>5.08 GB</t>
-  </si>
-  <si>
-    <t>4.64 GB</t>
-  </si>
-  <si>
-    <t>5.13 %</t>
-  </si>
-  <si>
-    <t>22.40 %</t>
-  </si>
-  <si>
-    <t>22.35 %</t>
-  </si>
-  <si>
-    <t>53.00 %</t>
-  </si>
-  <si>
-    <t>69.68 %</t>
+    <t>5.46 GB</t>
+  </si>
+  <si>
+    <t>SRFTPDR01</t>
+  </si>
+  <si>
+    <t>63.85 %</t>
+  </si>
+  <si>
+    <t>8.20 GB</t>
+  </si>
+  <si>
+    <t>3.52 GB</t>
+  </si>
+  <si>
+    <t>5.93 GB</t>
+  </si>
+  <si>
+    <t>10.74 %</t>
+  </si>
+  <si>
+    <t>51.29 %</t>
+  </si>
+  <si>
+    <t>12.08 GB</t>
   </si>
   <si>
     <t>IPS SALUD SURA INDUSTRIALES MEDELLIN</t>
   </si>
   <si>
+    <t>17.89 GB</t>
+  </si>
+  <si>
     <t>10.209.45.243</t>
   </si>
   <si>
-    <t>51.00 %</t>
-  </si>
-  <si>
-    <t>4.40 %</t>
+    <t>3.86 GB</t>
   </si>
   <si>
     <t>SRSAFIL03</t>
   </si>
   <si>
-    <t>5.70 GB</t>
-  </si>
-  <si>
-    <t>4.52 GB</t>
-  </si>
-  <si>
-    <t>65.89 %</t>
+    <t>3.66 GB</t>
+  </si>
+  <si>
+    <t>6.92 GB</t>
   </si>
   <si>
     <t>Operating System</t>
   </si>
   <si>
-    <t>1.48 %</t>
+    <t>4.12 GB</t>
+  </si>
+  <si>
+    <t>48.84 %</t>
+  </si>
+  <si>
+    <t>60.57 %</t>
   </si>
   <si>
     <t>DNPSCENTRALP01</t>
   </si>
   <si>
+    <t>3.56 %</t>
+  </si>
+  <si>
     <t>SRKMSP02</t>
   </si>
   <si>
-    <t>2.88 GB</t>
-  </si>
-  <si>
-    <t>6.57 GB</t>
+    <t>5.18 GB</t>
+  </si>
+  <si>
+    <t>4.60 %</t>
   </si>
   <si>
     <t>10.216.24.55</t>
   </si>
   <si>
-    <t>1.29 %</t>
-  </si>
-  <si>
-    <t>97.00 %</t>
-  </si>
-  <si>
     <t>SRAVBACP01</t>
   </si>
   <si>
-    <t>25.00 %</t>
-  </si>
-  <si>
-    <t>6.49 GB</t>
-  </si>
-  <si>
-    <t>2.61 %</t>
-  </si>
-  <si>
-    <t>14.59 GB</t>
-  </si>
-  <si>
-    <t>44.77 %</t>
-  </si>
-  <si>
-    <t>23.22 %</t>
+    <t>60.12 %</t>
+  </si>
+  <si>
+    <t>79.39 %</t>
+  </si>
+  <si>
+    <t>6.22 GB</t>
+  </si>
+  <si>
+    <t>31.42 GB</t>
   </si>
   <si>
     <t>Node</t>
   </si>
   <si>
-    <t>16.74 GB</t>
-  </si>
-  <si>
-    <t>5.47 GB</t>
-  </si>
-  <si>
-    <t>7.16 GB</t>
+    <t>58.00 %</t>
+  </si>
+  <si>
+    <t>37.50 %</t>
+  </si>
+  <si>
+    <t>47.65 GB</t>
+  </si>
+  <si>
+    <t>6.34 %</t>
+  </si>
+  <si>
+    <t>6.53 GB</t>
+  </si>
+  <si>
+    <t>12.54 %</t>
   </si>
   <si>
     <t>SRISSUINGCA01</t>
   </si>
   <si>
-    <t>7.91 GB</t>
-  </si>
-  <si>
-    <t>9.17 GB</t>
-  </si>
-  <si>
-    <t>8.75 GB</t>
+    <t>3.96 GB</t>
+  </si>
+  <si>
+    <t>22.07 GB</t>
   </si>
   <si>
     <t>Timestamp</t>
   </si>
   <si>
-    <t>76.07 %</t>
+    <t>88.00 %</t>
   </si>
   <si>
     <t>srbogcarptp01.suramericana.com.co</t>
   </si>
   <si>
+    <t>49.18 %</t>
+  </si>
+  <si>
+    <t>7.43 GB</t>
+  </si>
+  <si>
     <t>Peak Memory Used</t>
   </si>
   <si>
-    <t>5.68 GB</t>
-  </si>
-  <si>
     <t>SRM CAS CARIBE MEDELLIN</t>
   </si>
   <si>
-    <t>2.53 GB</t>
-  </si>
-  <si>
-    <t>43.74 %</t>
-  </si>
-  <si>
-    <t>3.78 GB</t>
+    <t>3.42 GB</t>
+  </si>
+  <si>
+    <t>10.203.90.57</t>
   </si>
   <si>
     <t>DNLISLBLNKSA01</t>
   </si>
   <si>
+    <t>2.79 GB</t>
+  </si>
+  <si>
+    <t>42.00 %</t>
+  </si>
+  <si>
     <t>10.205.30.56</t>
   </si>
   <si>
-    <t>5.27 GB</t>
-  </si>
-  <si>
-    <t>66.23 %</t>
-  </si>
-  <si>
-    <t>9.90 %</t>
-  </si>
-  <si>
-    <t>58.41 %</t>
-  </si>
-  <si>
-    <t>68.99 %</t>
-  </si>
-  <si>
-    <t>47.15 %</t>
+    <t>3.93 %</t>
+  </si>
+  <si>
+    <t>7.15 GB</t>
+  </si>
+  <si>
+    <t>9.94 GB</t>
+  </si>
+  <si>
+    <t>6.83 GB</t>
   </si>
   <si>
     <t>SRM TI VIVA ENVIGADO</t>
   </si>
   <si>
-    <t>2.62 GB</t>
+    <t>2.93 GB</t>
+  </si>
+  <si>
+    <t>1.10 %</t>
   </si>
   <si>
     <t>CPU Load - Memory Used for All Nodes (Domain Controllers) from Last Month</t>
   </si>
   <si>
-    <t>2.14 GB</t>
-  </si>
-  <si>
     <t>CENTRO DE COMPUTO MEDELLIN</t>
   </si>
   <si>
-    <t>SRSAFTP02_NEW</t>
-  </si>
-  <si>
-    <t>5.80 GB</t>
-  </si>
-  <si>
-    <t>34.27 %</t>
-  </si>
-  <si>
     <t>10.205.31.57</t>
   </si>
   <si>
-    <t>9.13 %</t>
-  </si>
-  <si>
     <t>10.207.24.231</t>
   </si>
   <si>
-    <t>21.19 GB</t>
-  </si>
-  <si>
-    <t>7.05 GB</t>
-  </si>
-  <si>
-    <t>34.00 %</t>
-  </si>
-  <si>
-    <t>3.61 GB</t>
+    <t>14.00 %</t>
+  </si>
+  <si>
+    <t>3.72 GB</t>
+  </si>
+  <si>
+    <t>3.63 GB</t>
+  </si>
+  <si>
+    <t>7.65 GB</t>
+  </si>
+  <si>
+    <t>4.25 GB</t>
   </si>
   <si>
     <t>Average CPU Load</t>
   </si>
   <si>
-    <t>6.03 GB</t>
-  </si>
-  <si>
-    <t>5.87 GB</t>
+    <t>56.00 %</t>
+  </si>
+  <si>
+    <t>7.24 %</t>
   </si>
   <si>
     <t>Windows 2025 Server</t>
   </si>
   <si>
-    <t>68.38 %</t>
-  </si>
-  <si>
-    <t>4.63 GB</t>
+    <t>8.92 GB</t>
+  </si>
+  <si>
+    <t>2.87 GB</t>
+  </si>
+  <si>
+    <t>3.30 GB</t>
   </si>
   <si>
     <t>77.00 %</t>
   </si>
   <si>
-    <t>6.89 GB</t>
+    <t>0.97 %</t>
+  </si>
+  <si>
+    <t>10.208.24.250</t>
   </si>
   <si>
     <t>80.00 %</t>
@@ -805,7 +859,10 @@
     <t>99.00 %</t>
   </si>
   <si>
-    <t>43.93 %</t>
+    <t>74.33 %</t>
+  </si>
+  <si>
+    <t>6.64 GB</t>
   </si>
 </sst>
 </file>
@@ -1150,1164 +1207,1269 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D4" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E4" t="s">
         <v>250</v>
       </c>
       <c r="F4" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="G4" t="s">
-        <v>200</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>150</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s">
-        <v>135</v>
+        <v>227</v>
       </c>
       <c r="J4" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="K4" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="F5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G5" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="K5" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>111</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="G6" t="s">
-        <v>123</v>
+        <v>189</v>
       </c>
       <c r="H6" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
       <c r="I6" t="s">
-        <v>55</v>
+        <v>243</v>
       </c>
       <c r="J6" t="s">
-        <v>244</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E7" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="F7" t="s">
-        <v>127</v>
+        <v>270</v>
       </c>
       <c r="G7" t="s">
-        <v>226</v>
+        <v>126</v>
       </c>
       <c r="H7" t="s">
-        <v>70</v>
+        <v>174</v>
       </c>
       <c r="I7" t="s">
-        <v>89</v>
+        <v>215</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>196</v>
       </c>
       <c r="K7" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>230</v>
       </c>
       <c r="F8" t="s">
-        <v>191</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s">
-        <v>84</v>
+        <v>274</v>
       </c>
       <c r="H8" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I8" t="s">
-        <v>88</v>
+        <v>221</v>
       </c>
       <c r="J8" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="K8" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G9" t="s">
+        <v>253</v>
+      </c>
+      <c r="H9" t="s">
+        <v>188</v>
+      </c>
+      <c r="I9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" t="s">
-        <v>255</v>
-      </c>
-      <c r="D9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" t="s">
-        <v>190</v>
-      </c>
-      <c r="F9" t="s">
-        <v>152</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" t="s">
-        <v>263</v>
-      </c>
       <c r="K9" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="C10" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>186</v>
+        <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="G10" t="s">
-        <v>253</v>
+        <v>130</v>
       </c>
       <c r="H10" t="s">
-        <v>8</v>
+        <v>188</v>
       </c>
       <c r="I10" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="J10" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="K10" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="C11" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>156</v>
+        <v>263</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>141</v>
       </c>
       <c r="G11" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="H11" t="s">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="I11" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
       <c r="J11" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="K11" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>206</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="H12" t="s">
-        <v>207</v>
+        <v>109</v>
       </c>
       <c r="I12" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="J12" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="K12" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" t="s">
         <v>230</v>
       </c>
-      <c r="C13" t="s">
-        <v>166</v>
-      </c>
-      <c r="D13" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" t="s">
-        <v>144</v>
-      </c>
       <c r="F13" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="G13" t="s">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="I13" t="s">
-        <v>194</v>
+        <v>140</v>
       </c>
       <c r="J13" t="s">
-        <v>172</v>
+        <v>53</v>
       </c>
       <c r="K13" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="E14" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="H14" t="s">
-        <v>116</v>
+        <v>254</v>
       </c>
       <c r="I14" t="s">
-        <v>218</v>
+        <v>272</v>
       </c>
       <c r="J14" t="s">
-        <v>58</v>
+        <v>281</v>
       </c>
       <c r="K14" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>280</v>
       </c>
       <c r="F15" t="s">
-        <v>7</v>
+        <v>156</v>
       </c>
       <c r="G15" t="s">
-        <v>165</v>
+        <v>68</v>
       </c>
       <c r="H15" t="s">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="I15" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="J15" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="K15" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
+        <v>280</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s">
-        <v>5</v>
+        <v>237</v>
       </c>
       <c r="H16" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="I16" t="s">
-        <v>63</v>
+        <v>198</v>
       </c>
       <c r="J16" t="s">
-        <v>236</v>
+        <v>138</v>
       </c>
       <c r="K16" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C17" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
-        <v>262</v>
+        <v>149</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="G17" t="s">
-        <v>104</v>
+        <v>249</v>
       </c>
       <c r="H17" t="s">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>254</v>
+        <v>47</v>
       </c>
       <c r="J17" t="s">
-        <v>54</v>
+        <v>158</v>
       </c>
       <c r="K17" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="C18" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="F18" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>115</v>
+        <v>257</v>
       </c>
       <c r="H18" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="I18" t="s">
-        <v>214</v>
+        <v>32</v>
       </c>
       <c r="J18" t="s">
-        <v>256</v>
+        <v>205</v>
       </c>
       <c r="K18" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
-        <v>136</v>
+        <v>280</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>67</v>
+        <v>180</v>
       </c>
       <c r="H19" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>255</v>
       </c>
       <c r="J19" t="s">
-        <v>235</v>
+        <v>146</v>
       </c>
       <c r="K19" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="F20" t="s">
         <v>154</v>
       </c>
       <c r="G20" t="s">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c r="H20" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="I20" t="s">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="J20" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="K20" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="F21" t="s">
-        <v>211</v>
+        <v>48</v>
       </c>
       <c r="G21" t="s">
-        <v>251</v>
+        <v>185</v>
       </c>
       <c r="H21" t="s">
-        <v>17</v>
+        <v>187</v>
       </c>
       <c r="I21" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J21" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="K21" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="B22" t="s">
-        <v>148</v>
+        <v>277</v>
       </c>
       <c r="C22" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="F22" t="s">
-        <v>33</v>
+        <v>204</v>
       </c>
       <c r="G22" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="H22" t="s">
-        <v>219</v>
+        <v>5</v>
       </c>
       <c r="I22" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="J22" t="s">
-        <v>210</v>
+        <v>102</v>
       </c>
       <c r="K22" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>199</v>
       </c>
       <c r="B23" t="s">
-        <v>247</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="F23" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G23" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="H23" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="J23" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="K23" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>216</v>
+        <v>99</v>
       </c>
       <c r="B24" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="C24" t="s">
+        <v>271</v>
+      </c>
+      <c r="D24" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" t="s">
+        <v>252</v>
+      </c>
+      <c r="G24" t="s">
+        <v>179</v>
+      </c>
+      <c r="H24" t="s">
+        <v>64</v>
+      </c>
+      <c r="I24" t="s">
+        <v>105</v>
+      </c>
+      <c r="J24" t="s">
         <v>166</v>
       </c>
-      <c r="D24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" t="s">
-        <v>260</v>
-      </c>
-      <c r="F24" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" t="s">
-        <v>201</v>
-      </c>
-      <c r="I24" t="s">
-        <v>6</v>
-      </c>
-      <c r="J24" t="s">
-        <v>175</v>
-      </c>
       <c r="K24" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>262</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="F25" t="s">
-        <v>4</v>
+        <v>216</v>
       </c>
       <c r="G25" t="s">
-        <v>138</v>
+        <v>46</v>
       </c>
       <c r="H25" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I25" t="s">
-        <v>124</v>
+        <v>212</v>
       </c>
       <c r="J25" t="s">
-        <v>234</v>
+        <v>119</v>
       </c>
       <c r="K25" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="C26" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E26" t="s">
-        <v>136</v>
+        <v>278</v>
       </c>
       <c r="F26" t="s">
-        <v>61</v>
+        <v>145</v>
       </c>
       <c r="G26" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="H26" t="s">
-        <v>27</v>
+        <v>266</v>
       </c>
       <c r="I26" t="s">
-        <v>249</v>
+        <v>17</v>
       </c>
       <c r="J26" t="s">
-        <v>28</v>
+        <v>152</v>
       </c>
       <c r="K26" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
-        <v>166</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
-        <v>96</v>
+        <v>280</v>
       </c>
       <c r="F27" t="s">
-        <v>1</v>
+        <v>222</v>
       </c>
       <c r="G27" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="H27" t="s">
-        <v>213</v>
+        <v>72</v>
       </c>
       <c r="I27" t="s">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="J27" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="K27" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>223</v>
       </c>
       <c r="C28" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D28" t="s">
-        <v>188</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="F28" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="G28" t="s">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="H28" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="I28" t="s">
-        <v>243</v>
+        <v>282</v>
       </c>
       <c r="J28" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="K28" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D29" t="s">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="F29" t="s">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s">
-        <v>181</v>
+        <v>23</v>
       </c>
       <c r="H29" t="s">
-        <v>20</v>
+        <v>208</v>
       </c>
       <c r="I29" t="s">
-        <v>75</v>
+        <v>206</v>
       </c>
       <c r="J29" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="K29" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>247</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>184</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="F30" t="s">
-        <v>246</v>
+        <v>182</v>
       </c>
       <c r="G30" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H30" t="s">
-        <v>34</v>
+        <v>228</v>
       </c>
       <c r="I30" t="s">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="J30" t="s">
-        <v>90</v>
+        <v>153</v>
       </c>
       <c r="K30" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D31" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="E31" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>208</v>
+        <v>258</v>
       </c>
       <c r="G31" t="s">
-        <v>240</v>
+        <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="I31" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J31" t="s">
-        <v>184</v>
+        <v>87</v>
       </c>
       <c r="K31" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>242</v>
+        <v>178</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>209</v>
       </c>
       <c r="C32" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D32" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="E32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F32" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="G32" t="s">
-        <v>99</v>
+        <v>246</v>
       </c>
       <c r="H32" t="s">
-        <v>257</v>
+        <v>191</v>
       </c>
       <c r="I32" t="s">
-        <v>151</v>
+        <v>25</v>
       </c>
       <c r="J32" t="s">
-        <v>185</v>
+        <v>55</v>
       </c>
       <c r="K32" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E33" t="s">
-        <v>136</v>
+        <v>280</v>
       </c>
       <c r="F33" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="G33" t="s">
-        <v>158</v>
+        <v>267</v>
       </c>
       <c r="H33" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="I33" t="s">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="J33" t="s">
-        <v>149</v>
+        <v>49</v>
       </c>
       <c r="K33" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>211</v>
+      </c>
+      <c r="B34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" t="s">
+        <v>260</v>
+      </c>
+      <c r="E34" t="s">
+        <v>269</v>
+      </c>
+      <c r="F34" t="s">
+        <v>157</v>
+      </c>
+      <c r="G34" t="s">
+        <v>159</v>
+      </c>
+      <c r="H34" t="s">
         <v>107</v>
       </c>
-      <c r="B34" t="s">
-        <v>261</v>
-      </c>
-      <c r="C34" t="s">
-        <v>166</v>
-      </c>
-      <c r="D34" t="s">
-        <v>81</v>
-      </c>
-      <c r="E34" t="s">
-        <v>136</v>
-      </c>
-      <c r="F34" t="s">
-        <v>132</v>
-      </c>
-      <c r="G34" t="s">
-        <v>238</v>
-      </c>
-      <c r="H34" t="s">
-        <v>228</v>
-      </c>
       <c r="I34" t="s">
-        <v>11</v>
+        <v>171</v>
       </c>
       <c r="J34" t="s">
-        <v>167</v>
+        <v>54</v>
       </c>
       <c r="K34" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>115</v>
+      </c>
+      <c r="C35" t="s">
+        <v>184</v>
       </c>
       <c r="D35" t="s">
-        <v>225</v>
+        <v>260</v>
       </c>
       <c r="E35" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="F35" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G35" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H35" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="I35" t="s">
-        <v>174</v>
+        <v>265</v>
       </c>
       <c r="J35" t="s">
+        <v>100</v>
+      </c>
+      <c r="K35" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>143</v>
+      </c>
+      <c r="B36" t="s">
+        <v>163</v>
+      </c>
+      <c r="C36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" t="s">
         <v>85</v>
       </c>
-      <c r="K35" t="s">
+      <c r="E36" t="s">
+        <v>280</v>
+      </c>
+      <c r="F36" t="s">
+        <v>3</v>
+      </c>
+      <c r="G36" t="s">
+        <v>273</v>
+      </c>
+      <c r="H36" t="s">
         <v>126</v>
+      </c>
+      <c r="I36" t="s">
+        <v>91</v>
+      </c>
+      <c r="J36" t="s">
+        <v>135</v>
+      </c>
+      <c r="K36" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" t="s">
+        <v>279</v>
+      </c>
+      <c r="C37" t="s">
+        <v>184</v>
+      </c>
+      <c r="D37" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" t="s">
+        <v>149</v>
+      </c>
+      <c r="F37" t="s">
+        <v>233</v>
+      </c>
+      <c r="G37" t="s">
+        <v>120</v>
+      </c>
+      <c r="H37" t="s">
+        <v>264</v>
+      </c>
+      <c r="I37" t="s">
+        <v>162</v>
+      </c>
+      <c r="J37" t="s">
+        <v>84</v>
+      </c>
+      <c r="K37" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" t="s">
+        <v>245</v>
+      </c>
+      <c r="E38" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" t="s">
+        <v>276</v>
+      </c>
+      <c r="G38" t="s">
+        <v>265</v>
+      </c>
+      <c r="H38" t="s">
+        <v>12</v>
+      </c>
+      <c r="I38" t="s">
+        <v>213</v>
+      </c>
+      <c r="J38" t="s">
+        <v>79</v>
+      </c>
+      <c r="K38" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
